--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1411,6 +1411,165 @@
         <v>0.6157790753592082</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:01:57.206545+00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5870537149973529</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3850653434857499</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2504183470634505</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5532136407126016</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5037057076205904</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1226428674722721</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4953461545598354</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4906904970721018</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6944561917883567</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7967430467784407</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2870432413723317</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.6663355979755337</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:01:57.206545+00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5702124185198038</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3655785789273447</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1962090286934781</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.456749738303713</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5117466734544206</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2033444095616081</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4598430446235039</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.3970496195276192</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6076298094323311</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8051131404924865</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4132723557799116</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.6279971673666702</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:01:57.206545+00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5749487626249928</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3562938482545149</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2505552585749934</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.4538084388659521</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4398132034146327</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1882869318421512</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4490054085748453</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4895021114529651</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5836987233597186</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.7686801473409888</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4171125724879096</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6157502584833824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -431,6 +431,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,60 +452,65 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>scorer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mAP50</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mAP50-95</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>mAP50-95_bike</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>mAP50-95_bus</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mAP50-95_car</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mAP50-95_motor</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mAP50-95_truck</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>mAP50_bike</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>mAP50_bus</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>mAP50_car</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>mAP50_motor</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mAP50_truck</t>
         </is>
@@ -526,40 +532,45 @@
           <t>val</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.305283855111676</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -579,40 +590,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.2985980425001021</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -632,40 +648,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.2671875716808476</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -685,40 +706,45 @@
           <t>val</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.305283855111676</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -738,40 +764,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.2985980425001021</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -791,40 +822,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.2671875716808476</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -844,40 +880,45 @@
           <t>val</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.305283855111676</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -897,40 +938,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.2985980425001021</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -950,40 +996,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.2671875716808476</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -1003,40 +1054,45 @@
           <t>val</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>0.305283855111676</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -1056,40 +1112,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.2985980425001021</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -1109,40 +1170,45 @@
           <t>val_day</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.2864582813916787</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.1694676058866271</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.05189771958791568</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.1375933791892869</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.4149946582734192</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.04768741669201867</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.1951648556904949</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.1375840949234592</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.1998616684221127</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.6864390943399843</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>0.1146779119947273</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.2937286372781098</v>
       </c>
     </row>
@@ -1162,40 +1228,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.2671875716808476</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -1215,40 +1286,45 @@
           <t>val</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.6168525926720191</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>0.3871220486009554</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.2728993601128687</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.4723224486552465</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.4889988640701858</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.23753290754277</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.4638566626237067</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>0.5494994340203249</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.6192393725406993</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.7994316043357315</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.4777788533656264</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.6383136990977132</v>
       </c>
     </row>
@@ -1268,40 +1344,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.5870626407171441</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.3850966070676673</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.2504239395832958</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.553226848239898</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.5036871387366137</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.1226428674722721</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>0.495502241306257</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>0.4906915445012149</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.6944839004141257</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.7967375435597949</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.2870432413723317</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.666356973738254</v>
       </c>
     </row>
@@ -1321,40 +1402,45 @@
           <t>val_day</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.5702934997512518</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.3655833267258713</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.1962456840831417</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.4565731490210802</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.5117632050880873</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>0.2035002850977668</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>0.4598343103392805</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>0.3970749033947613</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.6076061981997616</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.8051554078219201</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>0.4136205807263094</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>0.6280104086135064</v>
       </c>
     </row>
@@ -1374,40 +1460,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.5757243974868449</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.3563184614055295</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.2510302057586446</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>0.4537793114805136</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.4397865159026869</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>0.1880405810859183</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>0.448955692799884</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.493751576980352</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.5836455844003839</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0.768540287308475</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>0.4169054633858057</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>0.6157790753592082</v>
       </c>
     </row>
@@ -1427,40 +1518,45 @@
           <t>val_dawndusk</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.5870537149973529</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.3850653434857499</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.2504183470634505</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.5532136407126016</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.5037057076205904</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>0.1226428674722721</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.4953461545598354</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>0.4906904970721018</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.6944561917883567</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.7967430467784407</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>0.2870432413723317</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>0.6663355979755337</v>
       </c>
     </row>
@@ -1480,40 +1576,45 @@
           <t>val_day</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.5702124185198038</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.3655785789273447</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.1962090286934781</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.456749738303713</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.5117466734544206</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>0.2033444095616081</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.4598430446235039</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>0.3970496195276192</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.6076298094323311</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.8051131404924865</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>0.4132723557799116</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>0.6279971673666702</v>
       </c>
     </row>
@@ -1533,40 +1634,45 @@
           <t>val_night</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>0.5749487626249928</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.3562938482545149</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.2505552585749934</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>0.4538084388659521</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.4398132034146327</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.1882869318421512</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.4490054085748453</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>0.4895021114529651</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.5836987233597186</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.7686801473409888</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0.4171125724879096</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>0.6157502584833824</v>
       </c>
     </row>

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,52 +473,82 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>mAP75</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>mAP50-95_bike</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mAP50-95_bus</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mAP50-95_car</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mAP50-95_motor</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>mAP50-95_truck</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>mAP50_bike</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>mAP50_bus</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>mAP50_car</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mAP50_motor</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>mAP50_truck</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>mAP75_bike</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>mAP75_bus</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>mAP75_car</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>mAP75_motor</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>mAP75_truck</t>
         </is>
       </c>
     </row>
@@ -543,34 +579,34 @@
       <c r="F2" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -601,34 +637,34 @@
       <c r="F3" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -659,34 +695,34 @@
       <c r="F4" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -717,34 +753,34 @@
       <c r="F5" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -775,34 +811,34 @@
       <c r="F6" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -833,34 +869,34 @@
       <c r="F7" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -891,34 +927,34 @@
       <c r="F8" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -949,34 +985,34 @@
       <c r="F9" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -1007,34 +1043,34 @@
       <c r="F10" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -1065,34 +1101,34 @@
       <c r="F11" t="n">
         <v>0.1821077785312609</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.05857757516387878</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.1813013955302692</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.3960492167078498</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.08079940273686101</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.1938113025174458</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.1342899123969109</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.2571064233153138</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.6850911920463809</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.1523301078095831</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.2976016399901913</v>
       </c>
     </row>
@@ -1123,34 +1159,34 @@
       <c r="F12" t="n">
         <v>0.1790582554831355</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.05916335017802149</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.1893399994639595</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.4090397248020623</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.04000926950609535</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.1977389334655389</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.1719540059705934</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.26030617074089</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.6778656118585755</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.08098228770287202</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.3018821362275799</v>
       </c>
     </row>
@@ -1181,34 +1217,34 @@
       <c r="F13" t="n">
         <v>0.1694676058866271</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.05189771958791568</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.1375933791892869</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.4149946582734192</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.04768741669201867</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.1951648556904949</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.1375840949234592</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.1998616684221127</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>0.6864390943399843</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.1146779119947273</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.2937286372781098</v>
       </c>
     </row>
@@ -1239,34 +1275,34 @@
       <c r="F14" t="n">
         <v>0.1517324683726982</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.03837417500878087</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.1535417927400896</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.3502097366435195</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>0.01944927993295775</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0.1970873575381435</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.1115250288351943</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.2213794032452082</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.6520888007203838</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.05782666011861951</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.293117965484832</v>
       </c>
     </row>
@@ -1297,34 +1333,34 @@
       <c r="F15" t="n">
         <v>0.3871220486009554</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.2728993601128687</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.4723224486552465</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.4889988640701858</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.23753290754277</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>0.4638566626237067</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.5494994340203249</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.6192393725406993</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.7994316043357315</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.4777788533656264</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0.6383136990977132</v>
       </c>
     </row>
@@ -1355,34 +1391,34 @@
       <c r="F16" t="n">
         <v>0.3850966070676673</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.2504239395832958</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.553226848239898</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.5036871387366137</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>0.1226428674722721</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>0.495502241306257</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.4906915445012149</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.6944839004141257</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.7967375435597949</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.2870432413723317</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>0.666356973738254</v>
       </c>
     </row>
@@ -1413,34 +1449,34 @@
       <c r="F17" t="n">
         <v>0.3655833267258713</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.1962456840831417</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.4565731490210802</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>0.5117632050880873</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>0.2035002850977668</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>0.4598343103392805</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.3970749033947613</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.6076061981997616</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>0.8051554078219201</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>0.4136205807263094</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>0.6280104086135064</v>
       </c>
     </row>
@@ -1471,34 +1507,34 @@
       <c r="F18" t="n">
         <v>0.3563184614055295</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>0.2510302057586446</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.4537793114805136</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>0.4397865159026869</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>0.1880405810859183</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.448955692799884</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.493751576980352</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0.5836455844003839</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>0.768540287308475</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>0.4169054633858057</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>0.6157790753592082</v>
       </c>
     </row>
@@ -1529,34 +1565,34 @@
       <c r="F19" t="n">
         <v>0.3850653434857499</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.2504183470634505</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.5532136407126016</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>0.5037057076205904</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.1226428674722721</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>0.4953461545598354</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.4906904970721018</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.6944561917883567</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>0.7967430467784407</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>0.2870432413723317</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>0.6663355979755337</v>
       </c>
     </row>
@@ -1587,34 +1623,34 @@
       <c r="F20" t="n">
         <v>0.3655785789273447</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.1962090286934781</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.456749738303713</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>0.5117466734544206</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.2033444095616081</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>0.4598430446235039</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.3970496195276192</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.6076298094323311</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>0.8051131404924865</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>0.4132723557799116</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>0.6279971673666702</v>
       </c>
     </row>
@@ -1645,35 +1681,263 @@
       <c r="F21" t="n">
         <v>0.3562938482545149</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>0.2505552585749934</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.4538084388659521</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.4398132034146327</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.1882869318421512</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>0.4490054085748453</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.4895021114529651</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.5836987233597186</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0.7686801473409888</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>0.4171125724879096</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>0.6157502584833824</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:35:32.536079+00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5696099999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.3816</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.50209</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.12671</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.63143</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.79522</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.56167</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.11262</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.50192</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:35:32.536079+00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.53571</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.80101</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.37778</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.17977</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.16657</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.45921</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:35:32.536079+00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.54259</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.25695</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.17956</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.49232</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.51744</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.76758</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.54843</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.13437</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.45108</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1940,6 +1940,234 @@
         <v>0.45108</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:50:43.613339+00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5696099999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.3816</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.50209</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.12671</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.63143</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.79522</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.56167</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.11262</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.50192</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:50:43.613339+00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.53571</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.80101</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.37778</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.17977</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.16657</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.45921</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:50:43.613339+00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>set1_night_aug</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.54259</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.25695</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.17956</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.49232</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.51744</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.76758</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.54843</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.13437</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.45108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16T08:58:04.926074+00:00</t>
+          <t>2026-08-16T15:58:04.926074+07:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16T08:58:04.926074+00:00</t>
+          <t>2026-08-16T15:58:04.926074+07:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16T08:58:04.926074+00:00</t>
+          <t>2026-08-16T15:58:04.926074+07:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16T10:08:10.325959+00:00</t>
+          <t>2026-08-16T17:08:10.325959+07:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16T10:08:10.325959+00:00</t>
+          <t>2026-08-16T17:08:10.325959+07:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16T10:08:10.325959+00:00</t>
+          <t>2026-08-16T17:08:10.325959+07:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16T10:31:31.244659+00:00</t>
+          <t>2026-08-16T17:31:31.244659+07:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16T10:31:31.244659+00:00</t>
+          <t>2026-08-16T17:31:31.244659+07:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16T10:31:31.244659+00:00</t>
+          <t>2026-08-16T17:31:31.244659+07:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16T11:06:41.674227+00:00</t>
+          <t>2026-08-16T18:06:41.674227+07:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-16T11:06:41.674227+00:00</t>
+          <t>2026-08-16T18:06:41.674227+07:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16T11:06:41.674227+00:00</t>
+          <t>2026-08-16T18:06:41.674227+07:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-16T11:06:41.674227+00:00</t>
+          <t>2026-08-16T18:06:41.674227+07:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16T23:02:43.149658+00:00</t>
+          <t>2026-08-17T06:02:43.149658+07:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-16T23:02:43.149658+00:00</t>
+          <t>2026-08-17T06:02:43.149658+07:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-16T23:02:43.149658+00:00</t>
+          <t>2026-08-17T06:02:43.149658+07:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-16T23:02:43.149658+00:00</t>
+          <t>2026-08-17T06:02:43.149658+07:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-17T09:01:57.206545+00:00</t>
+          <t>2026-08-17T16:01:57.206545+07:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-17T09:01:57.206545+00:00</t>
+          <t>2026-08-17T16:01:57.206545+07:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17T09:01:57.206545+00:00</t>
+          <t>2026-08-17T16:01:57.206545+07:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-17T13:35:32.536079+00:00</t>
+          <t>2026-08-17T20:35:32.536079+07:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-17T13:35:32.536079+00:00</t>
+          <t>2026-08-17T20:35:32.536079+07:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17T13:35:32.536079+00:00</t>
+          <t>2026-08-17T20:35:32.536079+07:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-17T13:50:43.613339+00:00</t>
+          <t>2026-08-17T20:50:43.613339+07:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-17T13:50:43.613339+00:00</t>
+          <t>2026-08-17T20:50:43.613339+07:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-17T13:50:43.613339+00:00</t>
+          <t>2026-08-17T20:50:43.613339+07:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2168,466 @@
         <v>0.45108</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6290166871762756</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3879248275104588</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2662626646549935</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4896367552668121</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4890561980221793</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2220361758521236</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4726323437561858</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5550849154989284</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.644812820759741</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8017065209877553</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4949389470130463</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.6485402316219071</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5739</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.49398</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.10906</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.53986</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.79259</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.62714</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.19593</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.56733</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.08275</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.51703</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5936725988054097</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3792069376754245</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2499146090829722</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5410578391628323</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5034818400395269</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.103344649407855</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.4982357506839359</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5413691622448833</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.6788412769241348</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.798261522960853</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.266522421978956</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.6833686099182212</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.54074</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.19057</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.52241</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.80178</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.58751</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.16426</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.16174</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.4713</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5751452812440827</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3684171931407333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2012303387549844</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4569191494013737</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5117803038502275</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2080524271052469</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.4641037465918336</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.4199515462906319</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6065915696148365</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.8069196621888828</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.4093906309104882</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.6328729972155741</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.26329</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.18916</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.52967</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.54484</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.76705</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.22135</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.48224</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.14858</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.46724</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:52:27.117669+07:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>set3_combined</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.590378553540902</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3634675574651118</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2601215872754105</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4592141455315007</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4398332772041106</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.1987636292309836</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.4594051480835533</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5172139577944062</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.5986765551578269</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.7693044604374193</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4393614237990754</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.6273363705157824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_all_arms.xlsx
+++ b/results/metrics_all_arms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2628,6 +2628,466 @@
         <v>0.6273363705157824</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6211377471895654</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3881916372066783</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2926323994017329</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4781868521207343</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4859399267883859</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2219488698653111</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.4622501378572271</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.568249164159033</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.6347107900150926</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.7954777421863448</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.4722990045653206</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.6349520350220362</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5794899999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.49726</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.48983</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.54835</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.63885</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.79072</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.61219</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.20677</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.5581700000000001</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.16969</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.49767</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>val_dawndusk</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6192225660514005</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3967692993427563</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2913962806413527</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5393270374270898</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5002823138416271</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.1637243606512008</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.4891165041525107</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5995142657116006</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.6803138307498635</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.7935613363779257</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3548482311465845</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.6678751662710283</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.21947</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.49823</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.20631</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.51951</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.79856</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.18453</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.4594</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>val_day</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5828713740770771</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3697932207435066</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2203766506858792</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4475097094109509</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5080980770654246</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.215199516241052</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4577821503142263</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.4563961282768594</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.5972019253151639</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.8033414335397235</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4301192562251714</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.6272981270284681</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pycocotools</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.55864</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.20461</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.52571</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.76413</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.55145</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.4642</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.17079</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.44053</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:06:49.498916+07:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>method2_irfs_sampling</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>val_night</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ultralytics</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5914354177283965</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3664949844935789</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2708573816604956</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4536547507238907</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.4364345834706218</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2181463340160742</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.4533818725968125</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5165867259493104</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.5849725870558682</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.7644062748981453</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4676976057680022</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.6235138949706565</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
